--- a/Tables/Data/item.xlsx
+++ b/Tables/Data/item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>类别（Material/Consumable/Clue/Key）</t>
+          <t>类别（Material/Consumable/Clue/Key/Skin/Mask/Pass/Document）</t>
         </is>
       </c>
     </row>
@@ -723,6 +723,336 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>普通皮</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>皮,一次性</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>从妖民身上剥下的一层皮，边缘还带着温热的错觉。用一次就干裂。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>湿皮</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>皮,材料,水位刻度</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>溺者身上剥下的湿皮，皮上留着一道水位刻度。收服户绝民之后可与水痕合成钥匙。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>空白皮</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>皮,钥匙,材料</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>分福身身上剥下的、没有脸的皮。持有它可在弥勒教任意地区自由通行。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1201</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>查勘使面具</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>面具,跨阶段</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>查勘使的面具。戴上可直接制服老吏，到了龙窟也还认这个身份。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>泾龙面具</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>面具,合成</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>空白皮裹上泾龙丹结成的面具。持有它，钱塘君的战阵会少一层。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>牙</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>关键道具,跨阶段</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>从拾骨人的篮子里得到的牙。食教者与泾龙鬼都吃过龙，怕的就是这个。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>水痕</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>溺者溃散后留下的一圈水痕，干的边缘还能看出水位。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1501</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>泾龙丹</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>消耗品,合成</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>泾龙鬼腹中的丹丸。可用于伪装，也能与空白皮合成泾龙面具。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1601</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>名簿</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>文书</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>轮回堂核验用的名簿。纸页受潮，竖排的字迹一行行往下淌。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1701</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>进入废弃官署的钥匙</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>钥匙,合成</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>水痕与收服户绝民的湿皮合成的钥匙，能开废弃官署的门。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/Tables/Data/item.xlsx
+++ b/Tables/Data/item.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,336 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1801</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>活力药剂</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>消耗品,回复</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>恢复主角 50 点生命值。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>狂怒结晶</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>消耗品,怒气</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>主角怒气直接补满至 3 点。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1803</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>铁壁护符</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>消耗品,减伤</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>接下来 2 回合，主角受到全部伤害降低 40%。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>锐锋油膏</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>消耗品,增伤</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>接下来主角 3 次攻击，基础攻击力 + 7。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1805</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>浴血药剂</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>消耗品,吸血</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>接下来 3 回合，主角每次攻击命中后回复 12 点生命值。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1806</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>大瓶生命药剂</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>消耗品,回复</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>恢复主角 70 点生命值。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1807</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>瞬怒晶石</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>消耗品,怒气</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>立刻获得 2 点怒气。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>坚韧斗篷</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>消耗品,护盾</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>生成 1 层护盾，抵挡 1 次任意来源伤害。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1809</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>迅击粉末</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>消耗品,额外行动</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>本回合主角可以额外释放一次招式。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1810</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>固本甘露</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>消耗品,回春</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>接下来 3 回合，回合结束时主角回复 25 点生命值。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Tables/Data/item.xlsx
+++ b/Tables/Data/item.xlsx
@@ -1,146 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ebf4e27b32c487d"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-  </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="2">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="3">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -307,7 +302,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -316,13 +311,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -356,17 +351,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -421,110 +405,103 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t xml:space="preserve">quality</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>price</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t xml:space="preserve">tags</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t xml:space="preserve">desc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>道具 id（主键）</t>
+          <t xml:space="preserve">道具 id（主键）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>道具名</t>
+          <t xml:space="preserve">道具名</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>品质（Common/Rare/Epic）</t>
+          <t xml:space="preserve">品质（Common/Rare/Epic）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>售价（金币）</t>
+          <t xml:space="preserve">售价（金币）</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>标签，英文逗号分隔</t>
+          <t xml:space="preserve">标签，英文逗号分隔</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>描述（可空）</t>
+          <t xml:space="preserve">描述（可空）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>类别（Material/Consumable/Clue/Key/Skin/Mask/Pass/Document）</t>
+          <t xml:space="preserve">类别（Material/Consumable/Clue/Key/Skin/Mask/Pass/Document）</t>
         </is>
       </c>
     </row>
@@ -534,12 +511,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t xml:space="preserve">铁剑</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -547,17 +524,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>武器,近战</t>
+          <t xml:space="preserve">武器,近战</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>一把普通的铁剑，刃口有些钝了。</t>
+          <t xml:space="preserve">一把普通的铁剑，刃口有些钝了。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t xml:space="preserve">Material</t>
         </is>
       </c>
     </row>
@@ -567,12 +544,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>精钢长剑</t>
+          <t xml:space="preserve">精钢长剑</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -580,17 +557,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>武器,近战,锻造</t>
+          <t xml:space="preserve">武器,近战,锻造</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>锻造精良的长剑，剑身映得出人影。</t>
+          <t xml:space="preserve">锻造精良的长剑，剑身映得出人影。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t xml:space="preserve">Material</t>
         </is>
       </c>
     </row>
@@ -600,12 +577,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>龙鳞护甲</t>
+          <t xml:space="preserve">龙鳞护甲</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t xml:space="preserve">Epic</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -613,17 +590,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>防具,重甲</t>
+          <t xml:space="preserve">防具,重甲</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>用龙鳞缀成的护甲，沉得几乎穿不动。</t>
+          <t xml:space="preserve">用龙鳞缀成的护甲，沉得几乎穿不动。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t xml:space="preserve">Material</t>
         </is>
       </c>
     </row>
@@ -633,12 +610,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>治疗药水</t>
+          <t xml:space="preserve">治疗药水</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -646,17 +623,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>消耗品,回复</t>
+          <t xml:space="preserve">消耗品,回复</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>喝下去能缓过一口气。</t>
+          <t xml:space="preserve">喝下去能缓过一口气。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t xml:space="preserve">Consumable</t>
         </is>
       </c>
     </row>
@@ -666,12 +643,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>破旧信笺</t>
+          <t xml:space="preserve">破旧信笺</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -679,17 +656,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>线索</t>
+          <t xml:space="preserve">线索</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>字迹被水泡开，只认得出『镜』字</t>
+          <t xml:space="preserve">字迹被水泡开，只认得出『镜』字</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Clue</t>
+          <t xml:space="preserve">Clue</t>
         </is>
       </c>
     </row>
@@ -699,12 +676,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>铜镜碎片</t>
+          <t xml:space="preserve">铜镜碎片</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -712,17 +689,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>关键物</t>
+          <t xml:space="preserve">关键物</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>边缘还留着半个铭文</t>
+          <t xml:space="preserve">边缘还留着半个铭文</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t xml:space="preserve">Key</t>
         </is>
       </c>
     </row>
@@ -732,12 +709,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>普通皮</t>
+          <t xml:space="preserve">普通皮</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -745,17 +722,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>皮,一次性</t>
+          <t xml:space="preserve">皮,一次性</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>从妖民身上剥下的一层皮，边缘还带着温热的错觉。用一次就干裂。</t>
+          <t xml:space="preserve">从妖民身上剥下的一层皮，边缘还带着温热的错觉。用一次就干裂。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t xml:space="preserve">Skin</t>
         </is>
       </c>
     </row>
@@ -765,12 +742,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>湿皮</t>
+          <t xml:space="preserve">湿皮</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -778,17 +755,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>皮,材料,水位刻度</t>
+          <t xml:space="preserve">皮,材料,水位刻度</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>溺者身上剥下的湿皮，皮上留着一道水位刻度。收服户绝民之后可与水痕合成钥匙。</t>
+          <t xml:space="preserve">溺者身上剥下的湿皮，皮上留着一道水位刻度。收服户绝民之后可与水痕合成钥匙。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t xml:space="preserve">Skin</t>
         </is>
       </c>
     </row>
@@ -798,12 +775,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>空白皮</t>
+          <t xml:space="preserve">空白皮</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t xml:space="preserve">Epic</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -811,17 +788,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>皮,钥匙,材料</t>
+          <t xml:space="preserve">皮,钥匙,材料</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>分福身身上剥下的、没有脸的皮。持有它可在弥勒教任意地区自由通行。</t>
+          <t xml:space="preserve">分福身身上剥下的、没有脸的皮。持有它可在弥勒教任意地区自由通行。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t xml:space="preserve">Skin</t>
         </is>
       </c>
     </row>
@@ -831,12 +808,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>查勘使面具</t>
+          <t xml:space="preserve">查勘使面具</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -844,17 +821,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>面具,跨阶段</t>
+          <t xml:space="preserve">面具,跨阶段</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>查勘使的面具。戴上可直接制服老吏，到了龙窟也还认这个身份。</t>
+          <t xml:space="preserve">查勘使的面具。戴上可直接制服老吏，到了龙窟也还认这个身份。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t xml:space="preserve">Mask</t>
         </is>
       </c>
     </row>
@@ -864,12 +841,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>泾龙面具</t>
+          <t xml:space="preserve">泾龙面具</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t xml:space="preserve">Epic</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -877,17 +854,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>面具,合成</t>
+          <t xml:space="preserve">面具,合成</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>空白皮裹上泾龙丹结成的面具。持有它，钱塘君的战阵会少一层。</t>
+          <t xml:space="preserve">空白皮裹上泾龙丹结成的面具。持有它，钱塘君的战阵会少一层。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t xml:space="preserve">Mask</t>
         </is>
       </c>
     </row>
@@ -897,12 +874,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>牙</t>
+          <t xml:space="preserve">牙</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -910,17 +887,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>关键道具,跨阶段</t>
+          <t xml:space="preserve">关键道具,跨阶段</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>从拾骨人的篮子里得到的牙。食教者与泾龙鬼都吃过龙，怕的就是这个。</t>
+          <t xml:space="preserve">从拾骨人的篮子里得到的牙。食教者与泾龙鬼都吃过龙，怕的就是这个。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t xml:space="preserve">Key</t>
         </is>
       </c>
     </row>
@@ -930,12 +907,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>水痕</t>
+          <t xml:space="preserve">水痕</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -943,17 +920,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t xml:space="preserve">材料</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>溺者溃散后留下的一圈水痕，干的边缘还能看出水位。</t>
+          <t xml:space="preserve">溺者溃散后留下的一圈水痕，干的边缘还能看出水位。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t xml:space="preserve">Material</t>
         </is>
       </c>
     </row>
@@ -963,12 +940,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>泾龙丹</t>
+          <t xml:space="preserve">泾龙丹</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t xml:space="preserve">Epic</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -976,17 +953,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>消耗品,合成</t>
+          <t xml:space="preserve">消耗品,合成</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>泾龙鬼腹中的丹丸。可用于伪装，也能与空白皮合成泾龙面具。</t>
+          <t xml:space="preserve">泾龙鬼腹中的丹丸。可用于伪装，也能与空白皮合成泾龙面具。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t xml:space="preserve">Consumable</t>
         </is>
       </c>
     </row>
@@ -996,12 +973,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>名簿</t>
+          <t xml:space="preserve">名簿</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1009,17 +986,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>文书</t>
+          <t xml:space="preserve">文书</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>轮回堂核验用的名簿。纸页受潮，竖排的字迹一行行往下淌。</t>
+          <t xml:space="preserve">轮回堂核验用的名簿。纸页受潮，竖排的字迹一行行往下淌。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t xml:space="preserve">Document</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1006,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>进入废弃官署的钥匙</t>
+          <t xml:space="preserve">进入废弃官署的钥匙</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1042,351 +1019,687 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>钥匙,合成</t>
+          <t xml:space="preserve">钥匙,合成</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>水痕与收服户绝民的湿皮合成的钥匙，能开废弃官署的门。</t>
+          <t xml:space="preserve">水痕与收服户绝民的湿皮合成的钥匙，能开废弃官署的门。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t xml:space="preserve">Pass</t>
         </is>
       </c>
     </row>
     <row r="19">
+      <c r="A19"/>
       <c r="B19" t="n">
         <v>1801</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>活力药剂</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
+      <c r="C19" t="str">
+        <v>行头三样</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Common</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>消耗品,回复</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>恢复主角 50 点生命值。</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
+      <c r="F19" t="str">
+        <v>乔装,戏班</v>
+      </c>
+      <c r="G19" t="str">
+        <v>旧袍、油彩、小冠。戏班演奏达标后获得，用于酒肆乔装；通行不消耗。</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Key</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20"/>
       <c r="B20" t="n">
         <v>1802</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>狂怒结晶</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
+      <c r="C20" t="str">
+        <v>黑色长衫</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Common</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>消耗品,怒气</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>主角怒气直接补满至 3 点。</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
+      <c r="F20" t="str">
+        <v>乔装,衣肆</v>
+      </c>
+      <c r="G20" t="str">
+        <v>沉黑素面，袖口一线暗纹。以订衣人身份领取，用于酒肆乔装；通行不消耗。</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Key</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21"/>
       <c r="B21" t="n">
         <v>1803</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>铁壁护符</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
+      <c r="C21" t="str">
+        <v>金襟扣</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Common</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>消耗品,减伤</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>接下来 2 回合，主角受到全部伤害降低 40%。</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
+      <c r="F21" t="str">
+        <v>乔装,金饰</v>
+      </c>
+      <c r="G21" t="str">
+        <v>金银行打造的襟扣。乔装金饰需一枚，提交后获得；通行不消耗。</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Key</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22"/>
       <c r="B22" t="n">
         <v>1804</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>锐锋油膏</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
+      <c r="C22" t="str">
+        <v>金带钩</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Common</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>消耗品,增伤</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>接下来主角 3 次攻击，基础攻击力 + 7。</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
+      <c r="F22" t="str">
+        <v>乔装,金饰</v>
+      </c>
+      <c r="G22" t="str">
+        <v>金银行打造的带钩。乔装金饰需两枚，提交后获得；通行不消耗。</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Key</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23"/>
       <c r="B23" t="n">
         <v>1805</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="str">
+        <v>金环扣</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
+        <v>乔装,金饰</v>
+      </c>
+      <c r="G23" t="str">
+        <v>袖口与冠上的金环扣。乔装金饰需三枚，提交后获得；通行不消耗。</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Key</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24" t="n">
+        <v>1901</v>
+      </c>
+      <c r="C24" t="str">
+        <v>学徒皮</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G24" t="str">
+        <v>潜行绕背刺杀取得。使用后变为学徒，可重复使用。</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25"/>
+      <c r="B25" t="n">
+        <v>1902</v>
+      </c>
+      <c r="C25" t="str">
+        <v>都知皮</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G25" t="str">
+        <v>潜行绕背刺杀取得。使用后变为都知，可重复使用。</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26" t="n">
+        <v>1903</v>
+      </c>
+      <c r="C26" t="str">
+        <v>乐正皮</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G26" t="str">
+        <v>潜行绕背刺杀取得。使用后变为乐正，可重复使用。</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27"/>
+      <c r="B27" t="n">
+        <v>1904</v>
+      </c>
+      <c r="C27" t="str">
+        <v>顾客甲皮</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G27" t="str">
+        <v>潜行绕背刺杀取得。使用后变为顾客甲，可重复使用。</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28"/>
+      <c r="B28" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C28" t="str">
+        <v>顾客乙皮</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G28" t="str">
+        <v>潜行绕背刺杀取得。使用后变为顾客乙，可重复使用。</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29"/>
+      <c r="B29" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C29" t="str">
+        <v>顾客丙皮</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G29" t="str">
+        <v>潜行绕背刺杀取得。使用后变为顾客丙，可重复使用。</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30" t="n">
+        <v>1907</v>
+      </c>
+      <c r="C30" t="str">
+        <v>官证皮</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G30" t="str">
+        <v>潜行绕背刺杀取得。使用后变为官证，可重复使用。</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31"/>
+      <c r="B31" t="n">
+        <v>1908</v>
+      </c>
+      <c r="C31" t="str">
+        <v>金银匠皮</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G31" t="str">
+        <v>潜行绕背刺杀取得。使用后变为金银匠，可重复使用。</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32" t="n">
+        <v>1909</v>
+      </c>
+      <c r="C32" t="str">
+        <v>酒客皮</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Common</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="str">
+        <v>皮,身份</v>
+      </c>
+      <c r="G32" t="str">
+        <v>潜行绕背刺杀取得。使用后变为酒客，可重复使用。</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Skin</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>活力药剂</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>消耗品,回复</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>恢复主角 50 点生命值。</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>狂怒结晶</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>消耗品,怒气</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>主角怒气直接补满至 3 点。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>铁壁护符</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>消耗品,减伤</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>接下来 2 回合，主角受到全部伤害降低 40%。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>锐锋油膏</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>消耗品,增伤</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>接下来主角 3 次攻击，基础攻击力 + 7。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>浴血药剂</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>消耗品,吸血</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>接下来 3 回合，主角每次攻击命中后回复 12 点生命值。</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="n">
-        <v>1806</v>
-      </c>
-      <c r="C24" t="inlineStr">
+    <row r="38">
+      <c r="B38" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>大瓶生命药剂</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>消耗品,回复</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>恢复主角 70 点生命值。</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="n">
-        <v>1807</v>
-      </c>
-      <c r="C25" t="inlineStr">
+    <row r="39">
+      <c r="B39" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>瞬怒晶石</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>消耗品,怒气</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>立刻获得 2 点怒气。</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="n">
-        <v>1808</v>
-      </c>
-      <c r="C26" t="inlineStr">
+    <row r="40">
+      <c r="B40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>坚韧斗篷</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>消耗品,护盾</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>生成 1 层护盾，抵挡 1 次任意来源伤害。</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="n">
-        <v>1809</v>
-      </c>
-      <c r="C27" t="inlineStr">
+    <row r="41">
+      <c r="B41" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>迅击粉末</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>消耗品,额外行动</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>本回合主角可以额外释放一次招式。</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>1810</v>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="42">
+      <c r="B42" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>固本甘露</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>消耗品,回春</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>接下来 3 回合，回合结束时主角回复 25 点生命值。</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>